--- a/output/pdf_financials_xlsx/M.xlsx
+++ b/output/pdf_financials_xlsx/M.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.691268</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.952914</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.76294</v>
       </c>
     </row>
     <row r="93">
@@ -3077,7 +3077,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.691268</v>
       </c>

--- a/output/pdf_financials_xlsx/M.xlsx
+++ b/output/pdf_financials_xlsx/M.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008777999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026094</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038993</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.498575</v>
+        <v>-1.489797</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.684358</v>
+        <v>-3.658264</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.453181000000001</v>
+        <v>-8.414187999999999</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.498575</v>
+        <v>-1.489797</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.684358</v>
+        <v>-3.658264</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.453181000000001</v>
+        <v>-8.414187999999999</v>
       </c>
     </row>
     <row r="30">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/M.xlsx
+++ b/output/pdf_financials_xlsx/M.xlsx
@@ -4194,7 +4194,11 @@
           <t>Proceeds from shares issuable</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.06900000000000001</v>
       </c>
